--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
+++ b/main/ig/StructureDefinition-fr-core-patient-multiple-birth-r5.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
